--- a/resources/library/xlsx/restaurant-opening-checklist.xlsx
+++ b/resources/library/xlsx/restaurant-opening-checklist.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="1" r:id="R7893ecf122cf4625"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="Rdc1a4c1d80214d6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" r:id="Ra381a23515cb410f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="1" r:id="R2fa9dd3330424fe4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="R3aef8aed30ad4f5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" r:id="Rd5f02399478e4b1b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -165,6 +165,102 @@
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="7348aaaa-32af-4331-ae51-ddc649b04986"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R50bb32ee18d44d77"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="a0cc3518-ad8b-43a4-8bdc-ff4cec9132a0"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R63b25d6083f940b9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="14b134e3-301b-4958-9377-4ba6273575b4"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R92d0d7b0190a43bf"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -371,7 +467,7 @@
     <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="12"/>
       <x:c r="B1" s="12"/>
       <x:c r="C1" s="12"/>
@@ -1496,6 +1592,7 @@
     <x:mergeCell ref="A2:G2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1f33d1b34364620"/>
 </x:worksheet>
 </file>
 
@@ -1510,7 +1607,7 @@
     <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="12"/>
       <x:c r="B1" s="12"/>
       <x:c r="C1" s="12"/>
@@ -2571,6 +2668,7 @@
     <x:mergeCell ref="A2:F2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R87a14dbafab14a9a"/>
 </x:worksheet>
 </file>
 
@@ -2585,7 +2683,7 @@
     <x:col min="2" max="2" width="80" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="12"/>
       <x:c r="B1" s="12"/>
       <x:c r="C1" s="12"/>
@@ -3647,5 +3745,6 @@
     <x:mergeCell ref="A5:H5"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93013bb093ba4455"/>
 </x:worksheet>
 </file>